--- a/tame_output/ON/bt/strategyON_20230815.xlsx
+++ b/tame_output/ON/bt/strategyON_20230815.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>102.9%</t>
+          <t>103.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>139.6%</t>
+          <t>139.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>134.1%</t>
+          <t>134.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1689"/>
+  <dimension ref="A1:G1690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40357,7 +40357,7 @@
         <v>45151</v>
       </c>
       <c r="B1689" t="n">
-        <v>2.885475315628732</v>
+        <v>2.885506248482006</v>
       </c>
       <c r="C1689" t="n">
         <v>2.98583653611852</v>
@@ -40373,6 +40373,29 @@
       </c>
       <c r="G1689" t="n">
         <v>4.289845575110472</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="2" t="n">
+        <v>45152</v>
+      </c>
+      <c r="B1690" t="n">
+        <v>2.885216451676505</v>
+      </c>
+      <c r="C1690" t="n">
+        <v>2.989232987685216</v>
+      </c>
+      <c r="D1690" t="n">
+        <v>1.546589791732673</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>3.607512480064538</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>2.174737721309774</v>
+      </c>
+      <c r="G1690" t="n">
+        <v>4.294075620471082</v>
       </c>
     </row>
   </sheetData>
